--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N63_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N63_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.54711839079235</v>
+        <v>6.101406738503757</v>
       </c>
       <c r="D2" t="n">
-        <v>37.34028912752558</v>
+        <v>6.067796983222907</v>
       </c>
       <c r="E2" t="n">
-        <v>8.583157298551777</v>
+        <v>1.394763061014664</v>
       </c>
       <c r="F2" t="n">
-        <v>9.692115999316865</v>
+        <v>1.574968849888991</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.94503073897719</v>
+        <v>4.541067495083793</v>
       </c>
       <c r="D3" t="n">
-        <v>27.70253091176215</v>
+        <v>4.501661273161349</v>
       </c>
       <c r="E3" t="n">
-        <v>8.583157298551777</v>
+        <v>1.394763061014664</v>
       </c>
       <c r="F3" t="n">
-        <v>9.692115999316865</v>
+        <v>1.574968849888991</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.6486185235505</v>
+        <v>3.030400510076957</v>
       </c>
       <c r="D4" t="n">
-        <v>18.46189299037555</v>
+        <v>3.000057610936027</v>
       </c>
       <c r="E4" t="n">
-        <v>8.583157298551777</v>
+        <v>1.394763061014664</v>
       </c>
       <c r="F4" t="n">
-        <v>9.692115999316865</v>
+        <v>1.574968849888991</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.03372438967975</v>
+        <v>5.692980213322959</v>
       </c>
       <c r="D5" t="n">
-        <v>2.155471019358635</v>
+        <v>0.3502640406457782</v>
       </c>
       <c r="E5" t="n">
-        <v>8.583157298551777</v>
+        <v>1.394763061014664</v>
       </c>
       <c r="F5" t="n">
-        <v>9.692115999316865</v>
+        <v>1.574968849888991</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.17405272609323</v>
+        <v>4.253283567990151</v>
       </c>
       <c r="D6" t="n">
-        <v>24.53682040435467</v>
+        <v>3.987233315707634</v>
       </c>
       <c r="E6" t="n">
-        <v>8.583157298551777</v>
+        <v>1.394763061014664</v>
       </c>
       <c r="F6" t="n">
-        <v>9.692115999316865</v>
+        <v>1.574968849888991</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.70056674772373</v>
+        <v>3.688842096505106</v>
       </c>
       <c r="D7" t="n">
-        <v>17.95009406609106</v>
+        <v>2.916890285739797</v>
       </c>
       <c r="E7" t="n">
-        <v>8.583157298551777</v>
+        <v>1.394763061014664</v>
       </c>
       <c r="F7" t="n">
-        <v>9.692115999316865</v>
+        <v>1.574968849888991</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.28384528695335</v>
+        <v>6.383624859129919</v>
       </c>
       <c r="D8" t="n">
-        <v>17.79977374456164</v>
+        <v>2.892463233491267</v>
       </c>
       <c r="E8" t="n">
-        <v>8.583157298551777</v>
+        <v>1.394763061014664</v>
       </c>
       <c r="F8" t="n">
-        <v>9.692115999316865</v>
+        <v>1.574968849888991</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>13.73018897874012</v>
+        <v>2.23115570904527</v>
       </c>
       <c r="D9" t="n">
-        <v>13.5898296030838</v>
+        <v>2.208347310501118</v>
       </c>
       <c r="E9" t="n">
-        <v>8.583157298551777</v>
+        <v>1.394763061014664</v>
       </c>
       <c r="F9" t="n">
-        <v>9.692115999316865</v>
+        <v>1.574968849888991</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
